--- a/docs/importacion_constructoras_2026.xlsx
+++ b/docs/importacion_constructoras_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrique Arenas\Documents\Control de Entregas - Formatto\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70200DA-C3F9-4276-95E9-D3188CC300B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C8FBF-C3C7-424C-ABE7-51698E586C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29610" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
